--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,10 @@
     <t>ID</t>
   </si>
   <si>
-    <t>RequiredPerBar</t>
-  </si>
-  <si>
-    <t>MaxBar</t>
+    <t>ValuePerScale</t>
+  </si>
+  <si>
+    <t>TotalScale</t>
   </si>
   <si>
     <t>RewardSteps</t>
@@ -73,22 +73,22 @@
     <t>##</t>
   </si>
   <si>
-    <t>血条包ID</t>
-  </si>
-  <si>
-    <t>单条所需值</t>
-  </si>
-  <si>
-    <t>最大条数</t>
-  </si>
-  <si>
-    <t>奖励阶梯</t>
+    <t>肉条ID</t>
+  </si>
+  <si>
+    <t>单刻度所需值</t>
+  </si>
+  <si>
+    <t>总刻度数</t>
+  </si>
+  <si>
+    <t>肉条奖励阶梯</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>1:3,2|2:6,4|3:9,6|4:12,8|5:15,10</t>
+    <t>0:0,0|1:2,0|2:4,0|3:8,0|4:16,0|5:32,0</t>
   </si>
   <si>
     <t>示例</t>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
         <v>5</v>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -43,9 +43,6 @@
     <t>TotalScale</t>
   </si>
   <si>
-    <t>RewardSteps</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>(map#sep=:|),int,HuntingConfig.Bean.MeatProgressReward</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -82,16 +76,13 @@
     <t>总刻度数</t>
   </si>
   <si>
-    <t>肉条奖励阶梯</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
-    <t>0:0,0|1:2,0|2:4,0|3:8,0|4:16,0|5:32,0</t>
-  </si>
-  <si>
-    <t>示例</t>
+    <t>普通地图配置</t>
+  </si>
+  <si>
+    <t>隐藏地图配置</t>
   </si>
 </sst>
 </file>
@@ -1052,16 +1043,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="28.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="73.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="5" width="28.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1077,71 +1066,59 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6">
-      <c r="A3" s="2" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6">
+    <row r="5" ht="28" customHeight="1" spans="1:5">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>1</v>
@@ -1153,10 +1130,21 @@
         <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" spans="2:5">
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -67,7 +67,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>肉条ID</t>
+    <t>肉条配置ID</t>
   </si>
   <si>
     <t>单刻度所需值</t>
@@ -79,10 +79,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>普通地图配置</t>
-  </si>
-  <si>
-    <t>隐藏地图配置</t>
+    <t>肉条肉量获得上限 = 单刻度所需值 * 总刻度数</t>
   </si>
 </sst>
 </file>
@@ -254,7 +251,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,6 +260,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -448,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -463,6 +466,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -595,7 +611,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -607,119 +623,119 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -729,8 +745,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1043,8 +1074,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="28.625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
@@ -1102,49 +1133,35 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3">
+    <row r="5" ht="48" customHeight="1" spans="1:5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="3">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5" s="7">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="8" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" spans="2:5">
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
   </si>
   <si>
     <t>string</t>
@@ -735,7 +732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -752,12 +749,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,62 +1097,62 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:5">
       <c r="A5" s="5"/>
-      <c r="B5" s="6">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>40</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>16</v>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MeatProgress.xlsx
+++ b/Datas/MeatProgress.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>##var</t>
   </si>
@@ -43,16 +43,10 @@
     <t>TotalScale</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>##group</t>
@@ -71,12 +65,6 @@
   </si>
   <si>
     <t>总刻度数</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>肉条肉量获得上限 = 单刻度所需值 * 总刻度数</t>
   </si>
 </sst>
 </file>
@@ -732,7 +720,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -750,9 +738,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1065,14 +1050,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="5" width="28.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5">
+    <row r="1" ht="28" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1085,74 +1070,59 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+    <row r="4" ht="28" customHeight="1" spans="1:4">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1" spans="1:5">
+    <row r="5" ht="48" customHeight="1" spans="1:4">
       <c r="A5" s="5"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4">
         <v>5</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
